--- a/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов SARIMA.xlsx
+++ b/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов SARIMA.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -507,22 +507,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>92.15000000000001</v>
+        <v>40.98</v>
       </c>
       <c r="G2" t="n">
-        <v>72.70999999999999</v>
+        <v>40.1</v>
       </c>
       <c r="H2" t="n">
-        <v>10.49</v>
+        <v>6.32</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[539.61, 564.39, 589.88]</t>
+          <t>[467.26, 723.09, 758.36]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[544.33, 634.45, 733.22]</t>
+          <t>[495.67, 679.44, 710.13]</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -553,22 +553,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>93.28</v>
+        <v>53.75</v>
       </c>
       <c r="G3" t="n">
-        <v>81.89</v>
+        <v>53.56</v>
       </c>
       <c r="H3" t="n">
-        <v>11.76</v>
+        <v>7.31</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[566.56, 590.97, 650.59]</t>
+          <t>[738.59, 763.61, 795.02]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[634.45, 733.22, 686.11]</t>
+          <t>[679.44, 710.13, 843.07]</t>
         </is>
       </c>
     </row>
@@ -580,12 +580,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -599,22 +599,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>68.53</v>
+        <v>59.92</v>
       </c>
       <c r="G4" t="n">
-        <v>50.41</v>
+        <v>56.38</v>
       </c>
       <c r="H4" t="n">
-        <v>6.94</v>
+        <v>7.48</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[617.65, 661.28, 767.43]</t>
+          <t>[741.55, 786.54, 636.03]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[733.22, 686.11, 756.58]</t>
+          <t>[710.13, 843.07, 717.2]</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>38.55</v>
+        <v>75.13</v>
       </c>
       <c r="G5" t="n">
-        <v>36.46</v>
+        <v>74.83</v>
       </c>
       <c r="H5" t="n">
-        <v>4.72</v>
+        <v>10.57</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[707.82, 791.88, 773.0]</t>
+          <t>[774.91, 633.13, 534.3]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[686.11, 756.58, 825.36]</t>
+          <t>[843.07, 717.2, 606.56]</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -691,22 +691,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>35.87</v>
+        <v>136.4</v>
       </c>
       <c r="G6" t="n">
-        <v>29.37</v>
+        <v>116.34</v>
       </c>
       <c r="H6" t="n">
-        <v>3.82</v>
+        <v>15.66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[781.93, 769.0, 493.32]</t>
+          <t>[652.0, 539.76, 590.74]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[756.58, 825.36, 499.73]</t>
+          <t>[717.2, 606.56, 807.76]</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -737,22 +737,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>42.81</v>
+        <v>150.77</v>
       </c>
       <c r="G7" t="n">
-        <v>35.66</v>
+        <v>135.14</v>
       </c>
       <c r="H7" t="n">
-        <v>5.41</v>
+        <v>17.46</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[759.17, 491.27, 463.35]</t>
+          <t>[557.83, 596.2, 654.56]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[825.36, 499.73, 495.67]</t>
+          <t>[606.56, 807.76, 799.68]</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>30.21</v>
+        <v>154.72</v>
       </c>
       <c r="G8" t="n">
-        <v>25.6</v>
+        <v>152.33</v>
       </c>
       <c r="H8" t="n">
-        <v>4.35</v>
+        <v>18.98</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[505.16, 468.98, 724.13]</t>
+          <t>[617.1, 665.39, 666.37]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[499.73, 495.67, 679.44]</t>
+          <t>[807.76, 799.68, 798.4]</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -825,26 +825,26 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>40.98</v>
+        <v>53.65</v>
       </c>
       <c r="G9" t="n">
-        <v>40.1</v>
+        <v>47.07</v>
       </c>
       <c r="H9" t="n">
-        <v>6.32</v>
+        <v>5.85</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[467.26, 723.09, 758.36]</t>
+          <t>[779.25, 716.52, 781.04]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[495.67, 679.44, 710.13]</t>
+          <t>[799.68, 798.4, 819.95]</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -871,26 +871,26 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53.75</v>
+        <v>69.72</v>
       </c>
       <c r="G10" t="n">
-        <v>53.56</v>
+        <v>65.69</v>
       </c>
       <c r="H10" t="n">
-        <v>7.31</v>
+        <v>7.73</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[738.59, 763.61, 795.02]</t>
+          <t>[725.78, 785.69, 819.6]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[679.44, 710.13, 843.07]</t>
+          <t>[798.4, 819.95, 909.79]</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -917,26 +917,26 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>59.92</v>
+        <v>41.9</v>
       </c>
       <c r="G11" t="n">
-        <v>56.38</v>
+        <v>30.59</v>
       </c>
       <c r="H11" t="n">
-        <v>7.48</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[741.55, 786.54, 636.03]</t>
+          <t>[825.4, 839.14, 509.88]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[710.13, 843.07, 717.2]</t>
+          <t>[819.95, 909.79, 525.54]</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -967,22 +967,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>383.14</v>
+        <v>31.13</v>
       </c>
       <c r="G12" t="n">
-        <v>309.93</v>
+        <v>28.01</v>
       </c>
       <c r="H12" t="n">
-        <v>19.65</v>
+        <v>1.67</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[1000.46, 430.44, 2106.92]</t>
+          <t>[1545.38, 2005.13, 1724.26]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[1205.91, 531.99, 2729.71]</t>
+          <t>[1502.85, 1973.46, 1734.09]</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1013,22 +1013,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>285.56</v>
+        <v>29.39</v>
       </c>
       <c r="G13" t="n">
-        <v>247.85</v>
+        <v>24.83</v>
       </c>
       <c r="H13" t="n">
-        <v>13.73</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[477.25, 2338.34, 1497.79]</t>
+          <t>[1976.08, 1699.27, 2522.44]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[531.99, 2729.71, 1795.23]</t>
+          <t>[1973.46, 1734.09, 2559.49]</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1059,22 +1059,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>242.61</v>
+        <v>157.17</v>
       </c>
       <c r="G14" t="n">
-        <v>241.8</v>
+        <v>113.93</v>
       </c>
       <c r="H14" t="n">
-        <v>13.73</v>
+        <v>3.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[2460.25, 1571.53, 998.45]</t>
+          <t>[1698.11, 2520.71, 3958.62]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[2729.71, 1795.23, 1230.68]</t>
+          <t>[1734.09, 2559.49, 3691.59]</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>139.37</v>
+        <v>185.88</v>
       </c>
       <c r="G15" t="n">
-        <v>130.61</v>
+        <v>133.09</v>
       </c>
       <c r="H15" t="n">
-        <v>8.76</v>
+        <v>4.96</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[1652.34, 1047.62, 1849.19]</t>
+          <t>[2548.78, 4004.29, 1191.42]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[1795.23, 1230.68, 1915.07]</t>
+          <t>[2559.49, 3691.59, 1267.28]</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1151,22 +1151,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>81.53</v>
+        <v>191</v>
       </c>
       <c r="G16" t="n">
-        <v>65.38</v>
+        <v>137.76</v>
       </c>
       <c r="H16" t="n">
-        <v>5.16</v>
+        <v>5.95</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[1097.87, 1934.52, 1243.61]</t>
+          <t>[4013.71, 1194.12, 518.79]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[1230.68, 1915.07, 1199.71]</t>
+          <t>[3691.59, 1267.28, 536.79]</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>144.66</v>
+        <v>260.01</v>
       </c>
       <c r="G17" t="n">
-        <v>144.13</v>
+        <v>198.02</v>
       </c>
       <c r="H17" t="n">
-        <v>9.609999999999999</v>
+        <v>10.59</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[2060.62, 1328.0, 1661.4]</t>
+          <t>[1143.76, 497.55, 2498.32]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[1915.07, 1199.71, 1502.85]</t>
+          <t>[1267.28, 536.79, 2929.62]</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>88.48</v>
+        <v>176.25</v>
       </c>
       <c r="G18" t="n">
-        <v>88.02</v>
+        <v>129.11</v>
       </c>
       <c r="H18" t="n">
-        <v>5.77</v>
+        <v>5.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[1275.07, 1595.54, 2069.46]</t>
+          <t>[524.69, 2635.59, 1713.86]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[1199.71, 1502.85, 1973.46]</t>
+          <t>[536.79, 2929.62, 1795.06]</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>31.13</v>
+        <v>162.22</v>
       </c>
       <c r="G19" t="n">
-        <v>28.01</v>
+        <v>134.65</v>
       </c>
       <c r="H19" t="n">
-        <v>1.67</v>
+        <v>6.31</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[1545.38, 2005.13, 1724.26]</t>
+          <t>[2667.64, 1735.04, 1153.53]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[1502.85, 1973.46, 1734.09]</t>
+          <t>[2929.62, 1795.06, 1235.48]</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>29.39</v>
+        <v>43.8</v>
       </c>
       <c r="G20" t="n">
-        <v>24.83</v>
+        <v>38.02</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2</v>
+        <v>2.05</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[1976.08, 1699.27, 2522.44]</t>
+          <t>[1839.22, 1226.63, 1991.09]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[1973.46, 1734.09, 2559.49]</t>
+          <t>[1795.06, 1235.48, 2052.14]</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>157.17</v>
+        <v>49.97</v>
       </c>
       <c r="G21" t="n">
-        <v>113.93</v>
+        <v>37.93</v>
       </c>
       <c r="H21" t="n">
-        <v>3.61</v>
+        <v>2.18</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[1698.11, 2520.71, 3958.62]</t>
+          <t>[1210.74, 1969.45, 1250.41]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[1734.09, 2559.49, 3691.59]</t>
+          <t>[1235.48, 2052.14, 1244.06]</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1427,22 +1427,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>306.28</v>
+        <v>590.86</v>
       </c>
       <c r="G22" t="n">
-        <v>230.78</v>
+        <v>449.94</v>
       </c>
       <c r="H22" t="n">
-        <v>13.14</v>
+        <v>16.32</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[959.3, 544.23, 3148.51]</t>
+          <t>[2467.63, 3402.92, 1655.39]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[1063.19, 470.8, 3663.52]</t>
+          <t>[2521.78, 4370.94, 1327.73]</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>189.19</v>
+        <v>572.73</v>
       </c>
       <c r="G23" t="n">
-        <v>150.57</v>
+        <v>464.05</v>
       </c>
       <c r="H23" t="n">
-        <v>12.05</v>
+        <v>17.2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[580.05, 3356.63, 743.56]</t>
+          <t>[3450.79, 1677.75, 2790.93]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[470.8, 3663.52, 779.14]</t>
+          <t>[4370.94, 1327.73, 2912.92]</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1519,22 +1519,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>432.45</v>
+        <v>404.21</v>
       </c>
       <c r="G24" t="n">
-        <v>340.79</v>
+        <v>340.43</v>
       </c>
       <c r="H24" t="n">
-        <v>17.84</v>
+        <v>19.49</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[2947.04, 647.58, 846.84]</t>
+          <t>[1944.05, 3234.38, 8297.42]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[3663.52, 779.14, 1021.16]</t>
+          <t>[1327.73, 2912.92, 8213.9]</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1561,26 +1561,26 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>227.34</v>
+        <v>952.26</v>
       </c>
       <c r="G25" t="n">
-        <v>160.72</v>
+        <v>699.23</v>
       </c>
       <c r="H25" t="n">
-        <v>7.58</v>
+        <v>14.94</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[739.98, 966.09, 2759.88]</t>
+          <t>[2573.57, 6606.94, 962.19]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[779.14, 1021.16, 3147.81]</t>
+          <t>[2912.92, 8213.9, 1113.56]</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1607,26 +1607,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>195.45</v>
+        <v>641.2</v>
       </c>
       <c r="G26" t="n">
-        <v>157.81</v>
+        <v>413.45</v>
       </c>
       <c r="H26" t="n">
-        <v>9.09</v>
+        <v>10.33</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[995.47, 2841.16, 798.64]</t>
+          <t>[7107.48, 1034.46, 472.05]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[1021.16, 3147.81, 939.73]</t>
+          <t>[8213.9, 1113.56, 526.89]</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1653,26 +1653,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>250.7</v>
+        <v>55.28</v>
       </c>
       <c r="G27" t="n">
-        <v>237.05</v>
+        <v>39.77</v>
       </c>
       <c r="H27" t="n">
-        <v>11.56</v>
+        <v>2.05</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[2888.41, 811.92, 2197.85]</t>
+          <t>[1125.3, 513.36, 3816.45]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[3147.81, 939.73, 2521.78]</t>
+          <t>[1113.56, 526.89, 3722.4]</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1699,26 +1699,26 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>682.6900000000001</v>
+        <v>45.45</v>
       </c>
       <c r="G28" t="n">
-        <v>480.28</v>
+        <v>39.41</v>
       </c>
       <c r="H28" t="n">
-        <v>14.38</v>
+        <v>3.03</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[857.26, 2326.75, 3207.59]</t>
+          <t>[510.28, 3792.68, 806.66]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[939.73, 2521.78, 4370.94]</t>
+          <t>[526.89, 3722.4, 775.33]</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1745,26 +1745,26 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>590.86</v>
+        <v>120.46</v>
       </c>
       <c r="G29" t="n">
-        <v>449.94</v>
+        <v>111.21</v>
       </c>
       <c r="H29" t="n">
-        <v>16.32</v>
+        <v>8.51</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[2467.63, 3402.92, 1655.39]</t>
+          <t>[3861.55, 821.31, 1085.56]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[2521.78, 4370.94, 1327.73]</t>
+          <t>[3722.4, 775.33, 937.06]</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1791,26 +1791,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>572.73</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>464.05</v>
+        <v>60.63</v>
       </c>
       <c r="H30" t="n">
-        <v>17.2</v>
+        <v>5.97</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[3450.79, 1677.75, 2790.93]</t>
+          <t>[803.65, 1062.49, 3271.45]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[4370.94, 1327.73, 2912.92]</t>
+          <t>[775.33, 937.06, 3243.32]</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1837,26 +1837,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>404.21</v>
+        <v>64.02</v>
       </c>
       <c r="G31" t="n">
-        <v>340.43</v>
+        <v>49.51</v>
       </c>
       <c r="H31" t="n">
-        <v>19.49</v>
+        <v>4.29</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[1944.05, 3234.38, 8297.42]</t>
+          <t>[1040.65, 3204.19, 945.14]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[1327.73, 2912.92, 8213.9]</t>
+          <t>[937.06, 3243.32, 950.93]</t>
         </is>
       </c>
     </row>
@@ -1868,41 +1868,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>50.95</v>
+        <v>93.23</v>
       </c>
       <c r="G32" t="n">
-        <v>45.43</v>
+        <v>90.87</v>
       </c>
       <c r="H32" t="n">
-        <v>7.32</v>
+        <v>9.42</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[550.53, 599.56, 1067.17]</t>
+          <t>[1003.76, 895.12, 865.91]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[481.67, 585.47, 1013.82]</t>
+          <t>[921.73, 1014.74, 936.86]</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>29.3</v>
+        <v>155.58</v>
       </c>
       <c r="G33" t="n">
-        <v>24.01</v>
+        <v>149.99</v>
       </c>
       <c r="H33" t="n">
-        <v>3.25</v>
+        <v>17.86</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[548.95, 978.59, 770.67]</t>
+          <t>[867.74, 835.95, 915.74]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[585.47, 1013.82, 770.96]</t>
+          <t>[1014.74, 936.86, 713.69]</t>
         </is>
       </c>
     </row>
@@ -1960,41 +1960,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>21.66</v>
+        <v>145.47</v>
       </c>
       <c r="G34" t="n">
-        <v>19.97</v>
+        <v>90.63</v>
       </c>
       <c r="H34" t="n">
-        <v>2.44</v>
+        <v>12.44</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[990.2, 779.34, 743.55]</t>
+          <t>[917.78, 964.93, 1884.82]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[1013.82, 770.96, 715.65]</t>
+          <t>[936.86, 713.69, 1886.37]</t>
         </is>
       </c>
     </row>
@@ -2006,41 +2006,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>80.27</v>
+        <v>145.17</v>
       </c>
       <c r="G35" t="n">
-        <v>59.09</v>
+        <v>89.86</v>
       </c>
       <c r="H35" t="n">
-        <v>3.61</v>
+        <v>12.84</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[782.2, 746.59, 2536.26]</t>
+          <t>[964.62, 1883.26, 504.09]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[770.96, 715.65, 2671.34]</t>
+          <t>[713.69, 1886.37, 488.55]</t>
         </is>
       </c>
     </row>
@@ -2052,41 +2052,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>51.93</v>
+        <v>41.33</v>
       </c>
       <c r="G36" t="n">
-        <v>43.16</v>
+        <v>38.2</v>
       </c>
       <c r="H36" t="n">
-        <v>3.39</v>
+        <v>4.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[761.27, 2594.11, 727.81]</t>
+          <t>[1828.24, 508.1, 537.67]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[715.65, 2671.34, 734.44]</t>
+          <t>[1886.37, 488.55, 574.6]</t>
         </is>
       </c>
     </row>
@@ -2098,41 +2098,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>96.11</v>
+        <v>36.22</v>
       </c>
       <c r="G37" t="n">
-        <v>78.31999999999999</v>
+        <v>34.58</v>
       </c>
       <c r="H37" t="n">
-        <v>5.07</v>
+        <v>5.14</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[2514.87, 703.75, 969.52]</t>
+          <t>[508.19, 534.96, 942.36]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>[2671.34, 734.44, 921.73]</t>
+          <t>[488.55, 574.6, 986.83]</t>
         </is>
       </c>
     </row>
@@ -2144,41 +2144,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>84.18000000000001</v>
+        <v>52.95</v>
       </c>
       <c r="G38" t="n">
-        <v>70.31</v>
+        <v>50.63</v>
       </c>
       <c r="H38" t="n">
-        <v>7.31</v>
+        <v>6.62</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[724.99, 1001.54, 893.08]</t>
+          <t>[534.94, 947.17, 740.29]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>[734.44, 921.73, 1014.74]</t>
+          <t>[574.6, 986.83, 812.85]</t>
         </is>
       </c>
     </row>
@@ -2190,41 +2190,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>93.23</v>
+        <v>58.14</v>
       </c>
       <c r="G39" t="n">
-        <v>90.87</v>
+        <v>55.66</v>
       </c>
       <c r="H39" t="n">
-        <v>9.42</v>
+        <v>6.76</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[1003.76, 895.12, 865.91]</t>
+          <t>[951.01, 735.93, 701.69]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>[921.73, 1014.74, 936.86]</t>
+          <t>[986.83, 812.85, 755.93]</t>
         </is>
       </c>
     </row>
@@ -2236,41 +2236,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>155.58</v>
+        <v>245.98</v>
       </c>
       <c r="G40" t="n">
-        <v>149.99</v>
+        <v>182.47</v>
       </c>
       <c r="H40" t="n">
-        <v>17.86</v>
+        <v>10.26</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[867.74, 835.95, 915.74]</t>
+          <t>[737.21, 699.67, 2546.25]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>[1014.74, 936.86, 713.69]</t>
+          <t>[812.85, 755.93, 2961.75]</t>
         </is>
       </c>
     </row>
@@ -2282,41 +2282,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>145.47</v>
+        <v>252.77</v>
       </c>
       <c r="G41" t="n">
-        <v>90.63</v>
+        <v>170.88</v>
       </c>
       <c r="H41" t="n">
-        <v>12.44</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[917.78, 964.93, 1884.82]</t>
+          <t>[703.12, 2527.92, 718.45]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>[936.86, 713.69, 1886.37]</t>
+          <t>[755.93, 2961.75, 744.45]</t>
         </is>
       </c>
     </row>
@@ -2328,41 +2328,41 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>143.94</v>
+        <v>84.3</v>
       </c>
       <c r="G42" t="n">
-        <v>132.09</v>
+        <v>76.41</v>
       </c>
       <c r="H42" t="n">
-        <v>16.7</v>
+        <v>7.54</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[391.3, 612.24, 906.73]</t>
+          <t>[642.17, 1643.27, 914.69]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[463.04, 727.88, 1115.63]</t>
+          <t>[749.4, 1738.77, 941.21]</t>
         </is>
       </c>
     </row>
@@ -2374,41 +2374,41 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>64.31999999999999</v>
+        <v>66.33</v>
       </c>
       <c r="G43" t="n">
-        <v>53.66</v>
+        <v>66.28</v>
       </c>
       <c r="H43" t="n">
-        <v>5.65</v>
+        <v>5.14</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[684.51, 1014.33, 872.6]</t>
+          <t>[1805.23, 1010.56, 1422.14]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[727.88, 1115.63, 856.29]</t>
+          <t>[1738.77, 941.21, 1485.16]</t>
         </is>
       </c>
     </row>
@@ -2420,41 +2420,41 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>60.67</v>
+        <v>204.04</v>
       </c>
       <c r="G44" t="n">
-        <v>60.29</v>
+        <v>159.7</v>
       </c>
       <c r="H44" t="n">
-        <v>6.38</v>
+        <v>7.24</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[1056.57, 908.93, 967.92]</t>
+          <t>[986.41, 1388.04, 3581.35]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[1115.63, 856.29, 898.75]</t>
+          <t>[941.21, 1485.16, 3244.57]</t>
         </is>
       </c>
     </row>
@@ -2466,41 +2466,41 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>264.3</v>
+        <v>156.07</v>
       </c>
       <c r="G45" t="n">
-        <v>209</v>
+        <v>137.1</v>
       </c>
       <c r="H45" t="n">
-        <v>16.78</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[941.69, 1002.81, 1082.48]</t>
+          <t>[1347.79, 3472.86, 471.1]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[856.29, 898.75, 1520.02]</t>
+          <t>[1485.16, 3244.57, 516.73]</t>
         </is>
       </c>
     </row>
@@ -2512,41 +2512,41 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>365.69</v>
+        <v>265.21</v>
       </c>
       <c r="G46" t="n">
-        <v>309.88</v>
+        <v>180.06</v>
       </c>
       <c r="H46" t="n">
-        <v>21.73</v>
+        <v>9</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[940.7, 1024.06, 1012.65]</t>
+          <t>[3698.43, 499.09, 785.49]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[898.75, 1520.02, 1404.39]</t>
+          <t>[3244.57, 516.73, 716.8]</t>
         </is>
       </c>
     </row>
@@ -2558,41 +2558,41 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>426.83</v>
+        <v>49.9</v>
       </c>
       <c r="G47" t="n">
-        <v>417.23</v>
+        <v>43.87</v>
       </c>
       <c r="H47" t="n">
-        <v>35.09</v>
+        <v>6.21</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[994.46, 983.5, 444.15]</t>
+          <t>[459.4, 727.25, 1112.81]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[1520.02, 1404.39, 749.4]</t>
+          <t>[516.73, 716.8, 1048.98]</t>
         </is>
       </c>
     </row>
@@ -2604,17 +2604,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>137.74</v>
+        <v>112.61</v>
       </c>
       <c r="G48" t="n">
-        <v>125.65</v>
+        <v>106.77</v>
       </c>
       <c r="H48" t="n">
-        <v>10.73</v>
+        <v>11.99</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[1349.24, 620.91, 1545.46]</t>
+          <t>[777.84, 1197.46, 943.26]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[1404.39, 749.4, 1738.77]</t>
+          <t>[716.8, 1048.98, 832.48]</t>
         </is>
       </c>
     </row>
@@ -2650,17 +2650,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2669,22 +2669,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>84.3</v>
+        <v>62</v>
       </c>
       <c r="G49" t="n">
-        <v>76.41</v>
+        <v>51.18</v>
       </c>
       <c r="H49" t="n">
-        <v>7.54</v>
+        <v>5.4</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[642.17, 1643.27, 914.69]</t>
+          <t>[1136.73, 894.24, 950.67]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[749.4, 1738.77, 941.21]</t>
+          <t>[1048.98, 832.48, 946.63]</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2715,22 +2715,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>66.33</v>
+        <v>29.16</v>
       </c>
       <c r="G50" t="n">
-        <v>66.28</v>
+        <v>25.98</v>
       </c>
       <c r="H50" t="n">
-        <v>5.14</v>
+        <v>2.64</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[1805.23, 1010.56, 1422.14]</t>
+          <t>[849.55, 901.92, 1432.06]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[1738.77, 941.21, 1485.16]</t>
+          <t>[832.48, 946.63, 1415.91]</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2761,22 +2761,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>204.04</v>
+        <v>116.21</v>
       </c>
       <c r="G51" t="n">
-        <v>159.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>7.24</v>
+        <v>6.27</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[986.41, 1388.04, 3581.35]</t>
+          <t>[890.14, 1413.26, 1333.9]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[941.21, 1485.16, 3244.57]</t>
+          <t>[946.63, 1415.91, 1527.06]</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2803,26 +2803,26 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.23</v>
+        <v>0.82</v>
       </c>
       <c r="G52" t="n">
-        <v>0.13</v>
+        <v>0.47</v>
       </c>
       <c r="H52" t="n">
-        <v>1.535528993103181e+20</v>
+        <v>5.370529823496905e+19</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.09]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[0.0, 0.0, 1.5]</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2849,26 +2849,26 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="G53" t="n">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="H53" t="n">
-        <v>1.399421581836674e+20</v>
+        <v>9.712301652467945e+21</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.09, 0.12]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[0.4, 0.0, 0.4]</t>
+          <t>[0.0, 1.5, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2899,22 +2899,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.24</v>
+        <v>0.97</v>
       </c>
       <c r="G54" t="n">
-        <v>0.17</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>3.114439474133388e+19</v>
+        <v>9.239039596848223e+21</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.08, 0.12, 0.0]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.1]</t>
+          <t>[1.5, 0.0, 0.9]</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2945,22 +2945,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="G55" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="H55" t="n">
-        <v>99.84</v>
+        <v>9.537691479452152e+21</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.12, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>[0.4, 0.1, 0.3]</t>
+          <t>[0.0, 0.9, 0.6]</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="G56" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="H56" t="n">
-        <v>2.379980840234697e+17</v>
+        <v>2.838147640665854e+18</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>[0.1, 0.3, 0.0]</t>
+          <t>[0.9, 0.6, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3037,22 +3037,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H57" t="n">
-        <v>3.737010068659258e+17</v>
+        <v>6.347285314691734e+18</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>[0.3, 0.0, 0.0]</t>
+          <t>[0.6, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3089,11 +3089,11 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>5.915937339131991e+19</v>
+        <v>1.076132176671959e+19</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3129,22 +3129,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>5.370529823496905e+19</v>
+        <v>1.718786624996132e+20</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.09]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.5]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3175,22 +3175,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.82</v>
+        <v>2.89</v>
       </c>
       <c r="G60" t="n">
-        <v>0.51</v>
+        <v>1.67</v>
       </c>
       <c r="H60" t="n">
-        <v>9.712301652467945e+21</v>
+        <v>1.57744507731579e+20</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[0.0, 0.09, 0.12]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[0.0, 1.5, 0.0]</t>
+          <t>[0.0, 0.0, 5.0]</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3221,22 +3221,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.97</v>
+        <v>4.51</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.67</v>
       </c>
       <c r="H61" t="n">
-        <v>9.239039596848223e+21</v>
+        <v>1.379140487956975e+20</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[0.08, 0.12, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>[1.5, 0.0, 0.9]</t>
+          <t>[0.0, 5.0, 6.0]</t>
         </is>
       </c>
     </row>
@@ -3248,17 +3248,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3270,19 +3270,19 @@
         <v>0.18</v>
       </c>
       <c r="G62" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H62" t="n">
-        <v>9.59</v>
+        <v>8.5</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[0.68, 0.59, 0.98]</t>
+          <t>[2.3, 0.81, 0.87]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[0.7, 0.6, 1.3]</t>
+          <t>[2.0, 0.8, 0.8]</t>
         </is>
       </c>
     </row>
@@ -3294,17 +3294,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.19</v>
+        <v>0.03</v>
       </c>
       <c r="G63" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="H63" t="n">
-        <v>13.09</v>
+        <v>4.6</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[0.6, 0.99, 0.6]</t>
+          <t>[0.76, 0.83, 0.57]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>[0.6, 1.3, 0.7]</t>
+          <t>[0.8, 0.8, 0.6]</t>
         </is>
       </c>
     </row>
@@ -3340,17 +3340,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3359,22 +3359,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="G64" t="n">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="H64" t="n">
-        <v>17.6</v>
+        <v>4.51</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[0.99, 0.6, 0.77]</t>
+          <t>[0.85, 0.58, 1.04]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[1.3, 0.7, 0.9]</t>
+          <t>[0.8, 0.6, 1.0]</t>
         </is>
       </c>
     </row>
@@ -3386,17 +3386,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3411,16 +3411,16 @@
         <v>0.05</v>
       </c>
       <c r="H65" t="n">
-        <v>6.36</v>
+        <v>7.41</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[0.71, 0.88, 0.8]</t>
+          <t>[0.56, 1.01, 0.6]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[0.7, 0.9, 0.7]</t>
+          <t>[0.6, 1.0, 0.7]</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="G66" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H66" t="n">
-        <v>8.300000000000001</v>
+        <v>13.9</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[0.88, 0.82, 1.16]</t>
+          <t>[1.04, 0.61, 0.53]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>[0.9, 0.7, 1.1]</t>
+          <t>[1.0, 0.7, 0.7]</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3497,22 +3497,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="G67" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="H67" t="n">
-        <v>15.34</v>
+        <v>17.06</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[0.83, 1.17, 2.43]</t>
+          <t>[0.6, 0.52, 1.07]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>[0.7, 1.1, 2.0]</t>
+          <t>[0.7, 0.7, 1.2]</t>
         </is>
       </c>
     </row>
@@ -3524,17 +3524,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G68" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H68" t="n">
-        <v>6.04</v>
+        <v>16.74</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[1.05, 2.25, 0.81]</t>
+          <t>[0.56, 1.12, 0.62]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>[1.1, 2.0, 0.8]</t>
+          <t>[0.7, 1.2, 0.8]</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3589,22 +3589,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="G69" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="H69" t="n">
-        <v>8.5</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[2.3, 0.81, 0.87]</t>
+          <t>[1.24, 0.67, 0.84]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>[2.0, 0.8, 0.8]</t>
+          <t>[1.2, 0.8, 0.9]</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3635,22 +3635,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H70" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[0.76, 0.83, 0.57]</t>
+          <t>[0.66, 0.83, 0.66]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[0.8, 0.8, 0.6]</t>
+          <t>[0.8, 0.9, 0.7]</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3681,22 +3681,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G71" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H71" t="n">
-        <v>4.51</v>
+        <v>1.71</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[0.85, 0.58, 1.04]</t>
+          <t>[0.9, 0.71, 1.06]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>[0.8, 0.6, 1.0]</t>
+          <t>[0.9, 0.7, 1.1]</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3723,26 +3723,26 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>15.79</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>15.28</v>
+        <v>9.1</v>
       </c>
       <c r="H72" t="n">
-        <v>17.84</v>
+        <v>18.1</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[98.86, 62.47, 51.23]</t>
+          <t>[36.78, 41.02, 43.71]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>[118.5, 78.6, 61.3]</t>
+          <t>[43.3, 53.6, 51.9]</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3769,26 +3769,26 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>10.1</v>
+        <v>23.37</v>
       </c>
       <c r="G73" t="n">
-        <v>9.359999999999999</v>
+        <v>18.89</v>
       </c>
       <c r="H73" t="n">
-        <v>14.26</v>
+        <v>27.38</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[64.2, 52.89, 43.74]</t>
+          <t>[42.79, 44.31, 42.56]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[78.6, 61.3, 49.0]</t>
+          <t>[53.6, 51.9, 80.83]</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3815,26 +3815,26 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>8.119999999999999</v>
+        <v>32.38</v>
       </c>
       <c r="G74" t="n">
-        <v>7.94</v>
+        <v>27.94</v>
       </c>
       <c r="H74" t="n">
-        <v>15.51</v>
+        <v>25.13</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[55.74, 39.74, 39.5]</t>
+          <t>[46.97, 43.34, 170.72]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[61.3, 49.0, 48.5]</t>
+          <t>[51.9, 80.83, 212.13]</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3861,26 +3861,26 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>91.09</v>
+        <v>38.4</v>
       </c>
       <c r="G75" t="n">
-        <v>57.9</v>
+        <v>38.37</v>
       </c>
       <c r="H75" t="n">
-        <v>35.46</v>
+        <v>33.19</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[41.11, 40.02, 58.78]</t>
+          <t>[44.49, 172.13, 147.15]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>[49.0, 48.5, 216.12]</t>
+          <t>[80.83, 212.13, 108.39]</t>
         </is>
       </c>
     </row>
@@ -3892,41 +3892,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>89.90000000000001</v>
+        <v>45.39</v>
       </c>
       <c r="G76" t="n">
-        <v>54.29</v>
+        <v>30.74</v>
       </c>
       <c r="H76" t="n">
-        <v>29.44</v>
+        <v>28.71</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[46.85, 60.52, 49.01]</t>
+          <t>[217.42, 186.32, 85.72]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[48.5, 216.12, 43.4]</t>
+          <t>[212.13, 108.39, 76.72]</t>
         </is>
       </c>
     </row>
@@ -3938,41 +3938,41 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>89.66</v>
+        <v>44.91</v>
       </c>
       <c r="G77" t="n">
-        <v>54.22</v>
+        <v>29.56</v>
       </c>
       <c r="H77" t="n">
-        <v>29.68</v>
+        <v>28.97</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[60.94, 49.31, 41.73]</t>
+          <t>[185.64, 85.37, 66.33]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>[216.12, 43.4, 43.3]</t>
+          <t>[108.39, 76.72, 63.56]</t>
         </is>
       </c>
     </row>
@@ -3984,12 +3984,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4003,22 +4003,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>21.47</v>
+        <v>10.66</v>
       </c>
       <c r="G78" t="n">
-        <v>15.4</v>
+        <v>10.41</v>
       </c>
       <c r="H78" t="n">
-        <v>34.03</v>
+        <v>16.27</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[79.21, 43.67, 43.58]</t>
+          <t>[63.8, 52.6, 42.46]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[43.4, 43.3, 53.6]</t>
+          <t>[76.72, 63.56, 49.8]</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4049,22 +4049,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>9.449999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="G79" t="n">
-        <v>9.1</v>
+        <v>6.37</v>
       </c>
       <c r="H79" t="n">
-        <v>18.1</v>
+        <v>11.67</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[36.78, 41.02, 43.71]</t>
+          <t>[55.18, 43.1, 43.98]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>[43.3, 53.6, 51.9]</t>
+          <t>[63.56, 49.8, 48.0]</t>
         </is>
       </c>
     </row>
@@ -4076,17 +4076,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4095,22 +4095,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>23.37</v>
+        <v>34.15</v>
       </c>
       <c r="G80" t="n">
-        <v>18.89</v>
+        <v>20.71</v>
       </c>
       <c r="H80" t="n">
-        <v>27.38</v>
+        <v>25.24</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[42.79, 44.31, 42.56]</t>
+          <t>[48.98, 50.22, 144.21]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>[53.6, 51.9, 80.83]</t>
+          <t>[49.8, 48.0, 85.1]</t>
         </is>
       </c>
     </row>
@@ -4122,17 +4122,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4141,22 +4141,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>32.38</v>
+        <v>59.57</v>
       </c>
       <c r="G81" t="n">
-        <v>27.94</v>
+        <v>48.69</v>
       </c>
       <c r="H81" t="n">
-        <v>25.13</v>
+        <v>46.84</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[46.97, 43.34, 170.72]</t>
+          <t>[50.35, 144.44, 43.64]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>[51.9, 80.83, 212.13]</t>
+          <t>[48.0, 85.1, 128.01]</t>
         </is>
       </c>
     </row>
@@ -4168,17 +4168,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(4, 1, 0)</t>
+          <t>(4, 1, 1)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4187,22 +4187,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>154.81</v>
+        <v>193.06</v>
       </c>
       <c r="G82" t="n">
-        <v>152.21</v>
+        <v>179.92</v>
       </c>
       <c r="H82" t="n">
-        <v>7.9</v>
+        <v>6.17</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[1700.74, 1688.76, 1949.02]</t>
+          <t>[2304.95, 3062.68, 3842.99]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>[1890.85, 1811.02, 2093.26]</t>
+          <t>[2216.19, 2803.71, 3650.97]</t>
         </is>
       </c>
     </row>
@@ -4214,17 +4214,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>(4, 1, 1)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4233,22 +4233,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>152.99</v>
+        <v>125.02</v>
       </c>
       <c r="G83" t="n">
-        <v>110.5</v>
+        <v>109.75</v>
       </c>
       <c r="H83" t="n">
-        <v>5.29</v>
+        <v>3.49</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[1833.47, 2043.51, 1856.7]</t>
+          <t>[2981.02, 3771.16, 3814.2]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>[1811.02, 2093.26, 2116.01]</t>
+          <t>[2803.71, 3650.97, 3782.45]</t>
         </is>
       </c>
     </row>
@@ -4260,17 +4260,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(4, 1, 1)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4279,22 +4279,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>247.24</v>
+        <v>194.16</v>
       </c>
       <c r="G84" t="n">
-        <v>220.18</v>
+        <v>130.07</v>
       </c>
       <c r="H84" t="n">
-        <v>9.4</v>
+        <v>2.87</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[2027.48, 1851.63, 2297.19]</t>
+          <t>[3631.36, 3745.55, 4361.8]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>[2093.26, 2116.01, 2627.58]</t>
+          <t>[3650.97, 3782.45, 4695.5]</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4325,22 +4325,22 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>260.25</v>
+        <v>210.12</v>
       </c>
       <c r="G85" t="n">
-        <v>257.18</v>
+        <v>163.82</v>
       </c>
       <c r="H85" t="n">
-        <v>9.140000000000001</v>
+        <v>5.06</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[1890.23, 2314.19, 4583.31]</t>
+          <t>[3770.12, 4362.36, 1734.48]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[2116.01, 2627.58, 4815.7]</t>
+          <t>[3782.45, 4695.5, 1880.47]</t>
         </is>
       </c>
     </row>
@@ -4352,17 +4352,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>(4, 1, 1)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4371,22 +4371,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>114.07</v>
+        <v>205.88</v>
       </c>
       <c r="G86" t="n">
-        <v>103.31</v>
+        <v>185.93</v>
       </c>
       <c r="H86" t="n">
-        <v>3.3</v>
+        <v>6.68</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[2472.08, 4700.18, 2482.43]</t>
+          <t>[4386.03, 1739.65, 1698.77]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[2627.58, 4815.7, 2443.5]</t>
+          <t>[4695.5, 1880.47, 1806.25]</t>
         </is>
       </c>
     </row>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(4, 1, 1)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4417,22 +4417,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>101.86</v>
+        <v>76.63</v>
       </c>
       <c r="G87" t="n">
-        <v>94.28</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[4869.89, 2525.78, 2362.54]</t>
+          <t>[1814.8, 1734.64, 2019.08]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[4815.7, 2443.5, 2216.19]</t>
+          <t>[1880.47, 1806.25, 2109.5]</t>
         </is>
       </c>
     </row>
@@ -4444,17 +4444,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(4, 1, 1)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4463,22 +4463,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>185.31</v>
+        <v>57.75</v>
       </c>
       <c r="G88" t="n">
-        <v>163.09</v>
+        <v>55.55</v>
       </c>
       <c r="H88" t="n">
-        <v>6.38</v>
+        <v>2.73</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[2510.26, 2359.23, 3083.17]</t>
+          <t>[1772.99, 2041.89, 2036.32]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>[2443.5, 2216.19, 2803.71]</t>
+          <t>[1806.25, 2109.5, 2102.1]</t>
         </is>
       </c>
     </row>
@@ -4490,17 +4490,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>(4, 1, 1)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4509,22 +4509,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>193.06</v>
+        <v>58.08</v>
       </c>
       <c r="G89" t="n">
-        <v>179.92</v>
+        <v>56.91</v>
       </c>
       <c r="H89" t="n">
-        <v>6.17</v>
+        <v>2.54</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[2304.95, 3062.68, 3842.99]</t>
+          <t>[2065.63, 2047.3, 2527.46]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>[2216.19, 2803.71, 3650.97]</t>
+          <t>[2109.5, 2102.1, 2455.4]</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4555,22 +4555,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>125.02</v>
+        <v>63.49</v>
       </c>
       <c r="G90" t="n">
-        <v>109.75</v>
+        <v>58.25</v>
       </c>
       <c r="H90" t="n">
-        <v>3.49</v>
+        <v>2.05</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[2981.02, 3771.16, 3814.2]</t>
+          <t>[2074.65, 2544.74, 4746.06]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>[2803.71, 3650.97, 3782.45]</t>
+          <t>[2102.1, 2455.4, 4804.0]</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4601,22 +4601,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>194.16</v>
+        <v>68.89</v>
       </c>
       <c r="G91" t="n">
-        <v>130.07</v>
+        <v>56.89</v>
       </c>
       <c r="H91" t="n">
-        <v>2.87</v>
+        <v>2.07</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[3631.36, 3745.55, 4361.8]</t>
+          <t>[2566.51, 4766.56, 2452.98]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>[3650.97, 3782.45, 4695.5]</t>
+          <t>[2455.4, 4804.0, 2430.85]</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4643,26 +4643,26 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>52.23</v>
+        <v>62.6</v>
       </c>
       <c r="G92" t="n">
-        <v>47.19</v>
+        <v>61.31</v>
       </c>
       <c r="H92" t="n">
-        <v>6.31</v>
+        <v>3.64</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[570.08, 544.7, 963.46]</t>
+          <t>[1724.88, 1459.29, 1662.62]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>[586.05, 603.01, 1030.75]</t>
+          <t>[1783.24, 1506.79, 1740.69]</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4689,26 +4689,26 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>52.6</v>
+        <v>62.11</v>
       </c>
       <c r="G93" t="n">
-        <v>52.51</v>
+        <v>55.82</v>
       </c>
       <c r="H93" t="n">
-        <v>5.87</v>
+        <v>3.35</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[553.29, 973.91, 1277.72]</t>
+          <t>[1486.0, 1681.23, 1572.88]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>[603.01, 1030.75, 1328.7]</t>
+          <t>[1506.79, 1740.69, 1660.1]</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4720,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4739,22 +4739,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>36.2</v>
+        <v>111.52</v>
       </c>
       <c r="G94" t="n">
-        <v>25.68</v>
+        <v>98.59</v>
       </c>
       <c r="H94" t="n">
-        <v>1.74</v>
+        <v>4.29</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[1022.98, 1321.19, 1518.12]</t>
+          <t>[1694.33, 1580.43, 2969.83]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>[1030.75, 1328.7, 1579.88]</t>
+          <t>[1740.69, 1660.1, 3139.58]</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>62.6</v>
+        <v>88.92</v>
       </c>
       <c r="G95" t="n">
-        <v>50.33</v>
+        <v>71.38</v>
       </c>
       <c r="H95" t="n">
-        <v>2.67</v>
+        <v>3.51</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[1327.03, 1522.64, 2073.3]</t>
+          <t>[1604.01, 2996.98, 580.21]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>[1328.7, 1579.88, 2165.38]</t>
+          <t>[1660.1, 3139.58, 595.67]</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>74.97</v>
+        <v>54.03</v>
       </c>
       <c r="G96" t="n">
-        <v>73.59999999999999</v>
+        <v>43.78</v>
       </c>
       <c r="H96" t="n">
-        <v>4.27</v>
+        <v>3.37</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[1523.75, 2074.33, 1387.14]</t>
+          <t>[3054.17, 586.95, 592.13]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>[1579.88, 2165.38, 1460.76]</t>
+          <t>[3139.58, 595.67, 629.36]</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4877,22 +4877,22 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>70.42</v>
+        <v>46.11</v>
       </c>
       <c r="G97" t="n">
-        <v>67.23999999999999</v>
+        <v>35.1</v>
       </c>
       <c r="H97" t="n">
-        <v>3.84</v>
+        <v>3.93</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[2116.19, 1404.82, 1686.65]</t>
+          <t>[595.95, 597.65, 1019.82]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>[2165.38, 1460.76, 1783.24]</t>
+          <t>[595.67, 629.36, 1093.13]</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4923,22 +4923,22 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>63.28</v>
+        <v>49.88</v>
       </c>
       <c r="G98" t="n">
-        <v>60.54</v>
+        <v>45.9</v>
       </c>
       <c r="H98" t="n">
-        <v>3.76</v>
+        <v>4.73</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[1422.84, 1700.2, 1446.15]</t>
+          <t>[597.48, 1019.6, 1315.73]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>[1460.76, 1783.24, 1506.79]</t>
+          <t>[629.36, 1093.13, 1348.0]</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4969,22 +4969,22 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>62.6</v>
+        <v>32.84</v>
       </c>
       <c r="G99" t="n">
-        <v>61.31</v>
+        <v>29.23</v>
       </c>
       <c r="H99" t="n">
-        <v>3.64</v>
+        <v>2.28</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[1724.88, 1459.29, 1662.62]</t>
+          <t>[1049.58, 1339.45, 1575.13]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[1783.24, 1506.79, 1740.69]</t>
+          <t>[1093.13, 1348.0, 1610.72]</t>
         </is>
       </c>
     </row>
@@ -4996,41 +4996,41 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>62.11</v>
+        <v>33.88</v>
       </c>
       <c r="G100" t="n">
-        <v>55.82</v>
+        <v>27.12</v>
       </c>
       <c r="H100" t="n">
-        <v>3.35</v>
+        <v>1.52</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[1486.0, 1681.23, 1572.88]</t>
+          <t>[1378.42, 1609.95, 2188.3]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>[1506.79, 1740.69, 1660.1]</t>
+          <t>[1348.0, 1610.72, 2238.47]</t>
         </is>
       </c>
     </row>
@@ -5042,41 +5042,41 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>111.52</v>
+        <v>63.83</v>
       </c>
       <c r="G101" t="n">
-        <v>98.59</v>
+        <v>57.72</v>
       </c>
       <c r="H101" t="n">
-        <v>4.29</v>
+        <v>3.27</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[1694.33, 1580.43, 2969.83]</t>
+          <t>[1589.72, 2172.65, 1462.12]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>[1740.69, 1660.1, 3139.58]</t>
+          <t>[1610.72, 2238.47, 1548.44]</t>
         </is>
       </c>
     </row>
@@ -5088,41 +5088,41 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(2, 1, 5)</t>
+          <t>(2, 1, 0)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>116.76</v>
+        <v>68.03</v>
       </c>
       <c r="G102" t="n">
-        <v>114.2</v>
+        <v>60.13</v>
       </c>
       <c r="H102" t="n">
-        <v>21.06</v>
+        <v>5.31</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[349.0, 326.6, 700.27]</t>
+          <t>[798.37, 2472.87, 507.61]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>[428.9, 459.13, 830.45]</t>
+          <t>[884.19, 2552.15, 492.32]</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5149,26 +5149,26 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>57.71</v>
+        <v>55.14</v>
       </c>
       <c r="G103" t="n">
-        <v>45.56</v>
+        <v>43.9</v>
       </c>
       <c r="H103" t="n">
-        <v>8.74</v>
+        <v>3.87</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[367.42, 791.08, 366.68]</t>
+          <t>[2639.82, 529.64, 1106.37]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>[459.13, 830.45, 372.29]</t>
+          <t>[2552.15, 492.32, 1099.66]</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5195,26 +5195,26 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>115.39</v>
+        <v>49.41</v>
       </c>
       <c r="G104" t="n">
-        <v>96.62</v>
+        <v>40.8</v>
       </c>
       <c r="H104" t="n">
-        <v>12.1</v>
+        <v>3.46</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[884.59, 422.21, 1319.74]</t>
+          <t>[522.06, 1086.12, 2631.07]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>[830.45, 372.29, 1133.94]</t>
+          <t>[492.32, 1099.66, 2551.96]</t>
         </is>
       </c>
     </row>
@@ -5226,12 +5226,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5241,26 +5241,26 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>89.59999999999999</v>
+        <v>24.83</v>
       </c>
       <c r="G105" t="n">
-        <v>78.92</v>
+        <v>18.13</v>
       </c>
       <c r="H105" t="n">
-        <v>8.369999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[409.44, 1271.06, 1990.18]</t>
+          <t>[1058.38, 2550.87, 393.03]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>[372.29, 1133.94, 2052.66]</t>
+          <t>[1099.66, 2551.96, 381.0]</t>
         </is>
       </c>
     </row>
@@ -5272,17 +5272,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5291,22 +5291,22 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>88.31999999999999</v>
+        <v>60.52</v>
       </c>
       <c r="G106" t="n">
-        <v>74.34</v>
+        <v>57.1</v>
       </c>
       <c r="H106" t="n">
-        <v>5.28</v>
+        <v>9.27</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[1212.56, 1922.17, 530.98]</t>
+          <t>[2629.96, 411.05, 438.3]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>[1133.94, 2052.66, 544.87]</t>
+          <t>[2551.96, 381.0, 375.04]</t>
         </is>
       </c>
     </row>
@@ -5318,41 +5318,41 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>163.16</v>
+        <v>38.9</v>
       </c>
       <c r="G107" t="n">
-        <v>145.14</v>
+        <v>36.23</v>
       </c>
       <c r="H107" t="n">
-        <v>12.62</v>
+        <v>8.24</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[1814.05, 488.61, 743.62]</t>
+          <t>[405.38, 431.2, 809.41]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>[2052.66, 544.87, 884.19]</t>
+          <t>[381.0, 375.04, 837.54]</t>
         </is>
       </c>
     </row>
@@ -5364,41 +5364,41 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>(2, 1, 0)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>62.6</v>
+        <v>48.05</v>
       </c>
       <c r="G108" t="n">
-        <v>52.7</v>
+        <v>42.99</v>
       </c>
       <c r="H108" t="n">
-        <v>4.37</v>
+        <v>8.09</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[550.37, 801.54, 2482.2]</t>
+          <t>[415.89, 767.26, 339.89]</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>[544.87, 884.19, 2552.15]</t>
+          <t>[375.04, 837.54, 357.73]</t>
         </is>
       </c>
     </row>
@@ -5410,41 +5410,41 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>(2, 1, 0)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>68.03</v>
+        <v>103.55</v>
       </c>
       <c r="G109" t="n">
-        <v>60.13</v>
+        <v>93.83</v>
       </c>
       <c r="H109" t="n">
-        <v>5.31</v>
+        <v>11.65</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[798.37, 2472.87, 507.61]</t>
+          <t>[732.18, 322.38, 987.17]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>[884.19, 2552.15, 492.32]</t>
+          <t>[837.54, 357.73, 1127.95]</t>
         </is>
       </c>
     </row>
@@ -5456,17 +5456,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5475,22 +5475,22 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>55.14</v>
+        <v>70.45</v>
       </c>
       <c r="G110" t="n">
-        <v>43.9</v>
+        <v>62.08</v>
       </c>
       <c r="H110" t="n">
-        <v>3.87</v>
+        <v>5.26</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[2639.82, 529.64, 1106.37]</t>
+          <t>[340.77, 1055.1, 2014.21]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[2552.15, 492.32, 1099.66]</t>
+          <t>[357.73, 1127.95, 2110.63]</t>
         </is>
       </c>
     </row>
@@ -5502,17 +5502,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5521,22 +5521,22 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>49.41</v>
+        <v>42.35</v>
       </c>
       <c r="G111" t="n">
-        <v>40.8</v>
+        <v>40.32</v>
       </c>
       <c r="H111" t="n">
-        <v>3.46</v>
+        <v>3.67</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[522.06, 1086.12, 2631.07]</t>
+          <t>[1077.66, 2061.97, 540.07]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>[492.32, 1099.66, 2551.96]</t>
+          <t>[1127.95, 2110.63, 518.05]</t>
         </is>
       </c>
     </row>
@@ -5548,17 +5548,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5567,22 +5567,22 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>69.34999999999999</v>
+        <v>42.13</v>
       </c>
       <c r="G112" t="n">
-        <v>65.41</v>
+        <v>41.55</v>
       </c>
       <c r="H112" t="n">
-        <v>31.06</v>
+        <v>28.38</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[218.57, 91.76, 127.14]</t>
+          <t>[168.49, 204.64, 188.09]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>[315.08, 133.21, 185.42]</t>
+          <t>[136.33, 155.72, 144.52]</t>
         </is>
       </c>
     </row>
@@ -5594,41 +5594,41 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>(2, 1, 0)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>4.67</v>
+        <v>27</v>
       </c>
       <c r="G113" t="n">
-        <v>3.82</v>
+        <v>18</v>
       </c>
       <c r="H113" t="n">
-        <v>2.12</v>
+        <v>5.22</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[125.77, 186.45, 1384.39]</t>
+          <t>[161.6, 146.27, 481.28]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>[133.21, 185.42, 1381.39]</t>
+          <t>[155.72, 144.52, 434.93]</t>
         </is>
       </c>
     </row>
@@ -5640,17 +5640,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(3, 1, 2)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5659,22 +5659,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>21.65</v>
+        <v>56.18</v>
       </c>
       <c r="G114" t="n">
-        <v>16.42</v>
+        <v>46.3</v>
       </c>
       <c r="H114" t="n">
-        <v>5.12</v>
+        <v>14.71</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[182.8, 1417.18, 84.79]</t>
+          <t>[171.05, 526.12, 461.65]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[185.42, 1381.39, 95.65]</t>
+          <t>[144.52, 434.93, 440.47]</t>
         </is>
       </c>
     </row>
@@ -5686,41 +5686,41 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>51.16</v>
+        <v>31.14</v>
       </c>
       <c r="G115" t="n">
-        <v>44.12</v>
+        <v>28.74</v>
       </c>
       <c r="H115" t="n">
-        <v>17.92</v>
+        <v>7.38</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[1431.29, 85.74, 109.85]</t>
+          <t>[476.12, 453.03, 298.39]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>[1381.39, 95.65, 182.41]</t>
+          <t>[434.93, 440.47, 330.86]</t>
         </is>
       </c>
     </row>
@@ -5732,41 +5732,41 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>47.27</v>
+        <v>35.58</v>
       </c>
       <c r="G116" t="n">
-        <v>38.87</v>
+        <v>32.68</v>
       </c>
       <c r="H116" t="n">
-        <v>23.44</v>
+        <v>12.49</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[83.59, 106.77, 149.12]</t>
+          <t>[418.56, 278.29, 118.32]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>[95.65, 182.41, 178.03]</t>
+          <t>[440.47, 330.86, 141.87]</t>
         </is>
       </c>
     </row>
@@ -5778,41 +5778,41 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>38.72</v>
+        <v>25.92</v>
       </c>
       <c r="G117" t="n">
-        <v>29.02</v>
+        <v>22.23</v>
       </c>
       <c r="H117" t="n">
-        <v>16.54</v>
+        <v>9.92</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[117.2, 165.41, 145.57]</t>
+          <t>[290.89, 122.99, 171.21]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>[182.41, 178.03, 136.33]</t>
+          <t>[330.86, 141.87, 179.06]</t>
         </is>
       </c>
     </row>
@@ -5824,41 +5824,41 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>71.14</v>
+        <v>25.02</v>
       </c>
       <c r="G118" t="n">
-        <v>68.81999999999999</v>
+        <v>18.82</v>
       </c>
       <c r="H118" t="n">
-        <v>44.82</v>
+        <v>3.91</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[227.5, 200.49, 248.55]</t>
+          <t>[136.87, 188.53, 1392.0]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>[178.03, 136.33, 155.72]</t>
+          <t>[141.87, 179.06, 1433.99]</t>
         </is>
       </c>
     </row>
@@ -5870,41 +5870,41 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>42.13</v>
+        <v>31.49</v>
       </c>
       <c r="G119" t="n">
-        <v>41.55</v>
+        <v>25.03</v>
       </c>
       <c r="H119" t="n">
-        <v>28.38</v>
+        <v>14.56</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[168.49, 204.64, 188.09]</t>
+          <t>[194.14, 1425.75, 97.54]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>[136.33, 155.72, 144.52]</t>
+          <t>[179.06, 1433.99, 149.31]</t>
         </is>
       </c>
     </row>
@@ -5916,12 +5916,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5935,22 +5935,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>27</v>
+        <v>72.97</v>
       </c>
       <c r="G120" t="n">
-        <v>18</v>
+        <v>67.69</v>
       </c>
       <c r="H120" t="n">
-        <v>5.22</v>
+        <v>25.39</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[161.6, 146.27, 481.28]</t>
+          <t>[1329.06, 91.74, 174.5]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>[155.72, 144.52, 434.93]</t>
+          <t>[1433.99, 149.31, 133.92]</t>
         </is>
       </c>
     </row>
@@ -5962,41 +5962,41 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>(3, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>56.18</v>
+        <v>44.16</v>
       </c>
       <c r="G121" t="n">
-        <v>46.3</v>
+        <v>42.46</v>
       </c>
       <c r="H121" t="n">
-        <v>14.71</v>
+        <v>29.6</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[171.05, 526.12, 461.65]</t>
+          <t>[97.92, 184.59, 178.42]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>[144.52, 434.93, 440.47]</t>
+          <t>[149.31, 133.92, 153.09]</t>
         </is>
       </c>
     </row>
@@ -6008,12 +6008,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6023,26 +6023,26 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>49.9</v>
+        <v>103.85</v>
       </c>
       <c r="G122" t="n">
-        <v>47.19</v>
+        <v>94.63</v>
       </c>
       <c r="H122" t="n">
-        <v>9.57</v>
+        <v>14.7</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[466.2, 443.12, 407.55]</t>
+          <t>[558.91, 492.09, 544.26]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>[535.11, 473.04, 450.3]</t>
+          <t>[709.2, 579.41, 590.55]</t>
         </is>
       </c>
     </row>
@@ -6054,17 +6054,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6073,22 +6073,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>45.56</v>
+        <v>37.28</v>
       </c>
       <c r="G123" t="n">
-        <v>36.06</v>
+        <v>33.26</v>
       </c>
       <c r="H123" t="n">
-        <v>7.3</v>
+        <v>5.85</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[493.71, 437.94, 433.45]</t>
+          <t>[529.87, 580.46, 510.73]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>[473.04, 450.3, 508.6]</t>
+          <t>[579.41, 590.55, 550.88]</t>
         </is>
       </c>
     </row>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>54.08</v>
+        <v>102.24</v>
       </c>
       <c r="G124" t="n">
-        <v>47.95</v>
+        <v>71.13</v>
       </c>
       <c r="H124" t="n">
-        <v>9.279999999999999</v>
+        <v>13</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[426.48, 426.2, 629.43]</t>
+          <t>[601.11, 522.55, 718.6]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>[450.3, 508.6, 591.8]</t>
+          <t>[590.55, 550.88, 544.11]</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>52.88</v>
+        <v>102.47</v>
       </c>
       <c r="G125" t="n">
-        <v>51.13</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="H125" t="n">
-        <v>9.18</v>
+        <v>14.53</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[441.06, 643.14, 651.77]</t>
+          <t>[518.0, 715.43, 501.1]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>[508.6, 591.8, 617.25]</t>
+          <t>[550.88, 544.11, 533.78]</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6211,22 +6211,22 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>161.35</v>
+        <v>113.18</v>
       </c>
       <c r="G126" t="n">
-        <v>144</v>
+        <v>78.22</v>
       </c>
       <c r="H126" t="n">
-        <v>33.53</v>
+        <v>14.54</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[704.43, 692.01, 596.73]</t>
+          <t>[737.85, 508.04, 459.05]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>[591.8, 617.25, 352.14]</t>
+          <t>[544.11, 533.78, 474.22]</t>
         </is>
       </c>
     </row>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6253,26 +6253,26 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>121</v>
+        <v>48.54</v>
       </c>
       <c r="G127" t="n">
-        <v>80.73</v>
+        <v>42.73</v>
       </c>
       <c r="H127" t="n">
-        <v>21.28</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[620.89, 559.32, 740.56]</t>
+          <t>[459.11, 441.96, 422.03]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>[617.25, 352.14, 709.2]</t>
+          <t>[533.78, 474.22, 443.29]</t>
         </is>
       </c>
     </row>
@@ -6284,41 +6284,41 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>119.8</v>
+        <v>89.44</v>
       </c>
       <c r="G128" t="n">
-        <v>80.47</v>
+        <v>62.3</v>
       </c>
       <c r="H128" t="n">
-        <v>21.19</v>
+        <v>18.9</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[557.39, 739.01, 585.75]</t>
+          <t>[452.91, 430.62, 462.73]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>[352.14, 709.2, 579.41]</t>
+          <t>[474.22, 443.29, 309.81]</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6345,26 +6345,26 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>103.85</v>
+        <v>93.36</v>
       </c>
       <c r="G129" t="n">
-        <v>94.63</v>
+        <v>67.62</v>
       </c>
       <c r="H129" t="n">
-        <v>14.7</v>
+        <v>19.48</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[558.91, 492.09, 544.26]</t>
+          <t>[435.82, 466.68, 589.74]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>[709.2, 579.41, 590.55]</t>
+          <t>[443.29, 309.81, 628.26]</t>
         </is>
       </c>
     </row>
@@ -6376,41 +6376,41 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>37.28</v>
+        <v>106.84</v>
       </c>
       <c r="G130" t="n">
-        <v>33.26</v>
+        <v>94.02</v>
       </c>
       <c r="H130" t="n">
-        <v>5.85</v>
+        <v>24.57</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[529.87, 580.46, 510.73]</t>
+          <t>[469.96, 591.45, 611.8]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>[579.41, 590.55, 550.88]</t>
+          <t>[309.81, 628.26, 526.68]</t>
         </is>
       </c>
     </row>
@@ -6422,17 +6422,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 2)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6441,22 +6441,22 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>102.24</v>
+        <v>125.75</v>
       </c>
       <c r="G131" t="n">
-        <v>71.13</v>
+        <v>104.48</v>
       </c>
       <c r="H131" t="n">
-        <v>13</v>
+        <v>30.14</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[601.11, 522.55, 718.6]</t>
+          <t>[490.11, 519.62, 418.97]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>[590.55, 550.88, 544.11]</t>
+          <t>[628.26, 526.68, 250.73]</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6487,22 +6487,22 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>10.11</v>
+        <v>6.47</v>
       </c>
       <c r="G132" t="n">
-        <v>9.550000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="H132" t="n">
-        <v>6.96</v>
+        <v>1.84</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[163.83, 182.64, 93.99]</t>
+          <t>[209.16, 443.72, 310.02]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>[169.4, 192.02, 107.68]</t>
+          <t>[215.64, 452.73, 308.4]</t>
         </is>
       </c>
     </row>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6533,22 +6533,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>19.79</v>
+        <v>6.98</v>
       </c>
       <c r="G133" t="n">
-        <v>17.67</v>
+        <v>6.2</v>
       </c>
       <c r="H133" t="n">
-        <v>18.11</v>
+        <v>1.8</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[182.7, 94.02, 51.57]</t>
+          <t>[443.85, 310.11, 269.57]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>[192.02, 107.68, 81.6]</t>
+          <t>[452.73, 308.4, 277.6]</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6579,22 +6579,22 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>19.02</v>
+        <v>8.68</v>
       </c>
       <c r="G134" t="n">
-        <v>14.54</v>
+        <v>7.46</v>
       </c>
       <c r="H134" t="n">
-        <v>16.47</v>
+        <v>2.35</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[94.07, 51.6, 139.45]</t>
+          <t>[310.17, 269.63, 338.57]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>[107.68, 81.6, 139.45]</t>
+          <t>[308.4, 277.6, 351.2]</t>
         </is>
       </c>
     </row>
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6625,22 +6625,22 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>17.89</v>
+        <v>10.23</v>
       </c>
       <c r="G135" t="n">
-        <v>12.72</v>
+        <v>10.04</v>
       </c>
       <c r="H135" t="n">
-        <v>13.36</v>
+        <v>4.25</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[51.67, 139.64, 237.59]</t>
+          <t>[269.61, 338.55, 161.02]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>[81.6, 139.45, 245.63]</t>
+          <t>[277.6, 351.2, 151.54]</t>
         </is>
       </c>
     </row>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6671,22 +6671,22 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>5.75</v>
+        <v>17.08</v>
       </c>
       <c r="G136" t="n">
-        <v>4.95</v>
+        <v>15.7</v>
       </c>
       <c r="H136" t="n">
-        <v>2.26</v>
+        <v>8.58</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[140.28, 238.67, 202.89]</t>
+          <t>[338.65, 161.07, 182.57]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>[139.45, 245.63, 209.97]</t>
+          <t>[351.2, 151.54, 157.54]</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6717,22 +6717,22 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>6.89</v>
+        <v>22.79</v>
       </c>
       <c r="G137" t="n">
-        <v>6.89</v>
+        <v>21.2</v>
       </c>
       <c r="H137" t="n">
-        <v>3.09</v>
+        <v>14.76</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[238.66, 202.88, 209.03]</t>
+          <t>[161.12, 182.63, 102.42]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>[245.63, 209.97, 215.64]</t>
+          <t>[151.54, 157.54, 131.34]</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6763,22 +6763,22 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>7.66</v>
+        <v>26.86</v>
       </c>
       <c r="G138" t="n">
-        <v>7.58</v>
+        <v>26.81</v>
       </c>
       <c r="H138" t="n">
-        <v>2.8</v>
+        <v>29.89</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[202.94, 209.09, 443.58]</t>
+          <t>[182.53, 102.36, 77.57]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>[209.97, 215.64, 452.73]</t>
+          <t>[157.54, 131.34, 51.12]</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6809,22 +6809,22 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>6.47</v>
+        <v>22.67</v>
       </c>
       <c r="G139" t="n">
-        <v>5.7</v>
+        <v>18.49</v>
       </c>
       <c r="H139" t="n">
-        <v>1.84</v>
+        <v>24.57</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[209.16, 443.72, 310.02]</t>
+          <t>[102.22, 77.46, 132.38]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>[215.64, 452.73, 308.4]</t>
+          <t>[131.34, 51.12, 132.39]</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6836,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6855,22 +6855,22 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>6.98</v>
+        <v>21.44</v>
       </c>
       <c r="G140" t="n">
-        <v>6.2</v>
+        <v>17.6</v>
       </c>
       <c r="H140" t="n">
-        <v>1.8</v>
+        <v>21.54</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[443.85, 310.11, 269.57]</t>
+          <t>[77.64, 132.68, 233.71]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>[452.73, 308.4, 277.6]</t>
+          <t>[51.12, 132.39, 207.71]</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6901,22 +6901,22 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>8.68</v>
+        <v>19.34</v>
       </c>
       <c r="G141" t="n">
-        <v>7.46</v>
+        <v>15.83</v>
       </c>
       <c r="H141" t="n">
-        <v>2.35</v>
+        <v>8.26</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[310.17, 269.63, 338.57]</t>
+          <t>[132.19, 232.84, 199.03]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>[308.4, 277.6, 351.2]</t>
+          <t>[132.39, 207.71, 176.88]</t>
         </is>
       </c>
     </row>
@@ -6928,41 +6928,41 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1259.97</v>
+        <v>57.51</v>
       </c>
       <c r="G142" t="n">
-        <v>1197.32</v>
+        <v>42.39</v>
       </c>
       <c r="H142" t="n">
-        <v>160.54</v>
+        <v>2.61</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[2277.17, 2022.22, 2022.16]</t>
+          <t>[1824.96, 1632.51, 1334.84]</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>[590.07, 843.96, 1295.56]</t>
+          <t>[1823.93, 1726.94, 1366.53]</t>
         </is>
       </c>
     </row>
@@ -6974,41 +6974,41 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>691.34</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="G143" t="n">
-        <v>562.34</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="H143" t="n">
-        <v>57.31</v>
+        <v>4.73</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[1884.82, 1884.82, 1884.82]</t>
+          <t>[1682.87, 1465.96, 1836.46]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>[843.96, 1295.56, 1827.92]</t>
+          <t>[1726.94, 1366.53, 1920.41]</t>
         </is>
       </c>
     </row>
@@ -7020,41 +7020,41 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>309.22</v>
+        <v>151.41</v>
       </c>
       <c r="G144" t="n">
-        <v>221.94</v>
+        <v>121.77</v>
       </c>
       <c r="H144" t="n">
-        <v>16.24</v>
+        <v>3.83</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[1814.07, 1814.07, 1814.07]</t>
+          <t>[1417.06, 1986.45, 5974.82]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>[1295.56, 1827.92, 1680.62]</t>
+          <t>[1366.53, 1920.41, 5726.09]</t>
         </is>
       </c>
     </row>
@@ -7066,41 +7066,41 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1232.37</v>
+        <v>20.8</v>
       </c>
       <c r="G145" t="n">
-        <v>759.6</v>
+        <v>14</v>
       </c>
       <c r="H145" t="n">
-        <v>20.99</v>
+        <v>0.37</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[1786.52, 1786.52, 1786.52]</t>
+          <t>[1915.62, 5761.76, 610.69]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>[1827.92, 1680.62, 3918.02]</t>
+          <t>[1920.41, 5726.09, 612.23]</t>
         </is>
       </c>
     </row>
@@ -7112,41 +7112,41 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1231.23</v>
+        <v>26.18</v>
       </c>
       <c r="G146" t="n">
-        <v>753.22</v>
+        <v>15.6</v>
       </c>
       <c r="H146" t="n">
-        <v>20.67</v>
+        <v>0.33</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[1788.3, 1788.3, 1788.3]</t>
+          <t>[5771.42, 611.88, 875.07]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>[1680.62, 3918.02, 1766.04]</t>
+          <t>[5726.09, 612.23, 873.95]</t>
         </is>
       </c>
     </row>
@@ -7158,41 +7158,41 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>45.39</v>
+        <v>361.78</v>
       </c>
       <c r="G147" t="n">
-        <v>45.06</v>
+        <v>296.08</v>
       </c>
       <c r="H147" t="n">
-        <v>2.09</v>
+        <v>28.51</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[3875.77, 1713.3, 1783.76]</t>
+          <t>[738.6, 1046.96, 1894.53]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>[3918.02, 1766.04, 1823.93]</t>
+          <t>[612.23, 873.95, 1305.68]</t>
         </is>
       </c>
     </row>
@@ -7204,17 +7204,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7223,22 +7223,22 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>286.73</v>
+        <v>89.62</v>
       </c>
       <c r="G148" t="n">
-        <v>281.92</v>
+        <v>62.59</v>
       </c>
       <c r="H148" t="n">
-        <v>15.96</v>
+        <v>3.84</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[1427.97, 1611.76, 1431.42]</t>
+          <t>[873.12, 1341.61, 1892.29]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>[1766.04, 1823.93, 1726.94]</t>
+          <t>[873.95, 1305.68, 1741.28]</t>
         </is>
       </c>
     </row>
@@ -7250,17 +7250,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7269,22 +7269,22 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>57.51</v>
+        <v>177.79</v>
       </c>
       <c r="G149" t="n">
-        <v>42.39</v>
+        <v>151.41</v>
       </c>
       <c r="H149" t="n">
-        <v>2.61</v>
+        <v>8.26</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[1824.96, 1632.51, 1334.84]</t>
+          <t>[1342.47, 1893.69, 1741.22]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>[1823.93, 1726.94, 1366.53]</t>
+          <t>[1305.68, 1741.28, 2006.25]</t>
         </is>
       </c>
     </row>
@@ -7296,41 +7296,41 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>79.31999999999999</v>
+        <v>441</v>
       </c>
       <c r="G150" t="n">
-        <v>75.81999999999999</v>
+        <v>370.49</v>
       </c>
       <c r="H150" t="n">
-        <v>4.73</v>
+        <v>12.21</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[1682.87, 1465.96, 1836.46]</t>
+          <t>[1858.93, 1703.99, 3976.49]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>[1726.94, 1366.53, 1920.41]</t>
+          <t>[1741.28, 2006.25, 4668.04]</t>
         </is>
       </c>
     </row>
@@ -7342,17 +7342,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7361,22 +7361,22 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>151.41</v>
+        <v>680.36</v>
       </c>
       <c r="G151" t="n">
-        <v>121.77</v>
+        <v>646.92</v>
       </c>
       <c r="H151" t="n">
-        <v>3.83</v>
+        <v>34.45</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[1417.06, 1986.45, 5974.82]</t>
+          <t>[1630.57, 3778.75, 1706.57]</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>[1366.53, 1920.41, 5726.09]</t>
+          <t>[2006.25, 4668.04, 1030.78]</t>
         </is>
       </c>
     </row>
@@ -7388,41 +7388,41 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1187.51</v>
+        <v>121.62</v>
       </c>
       <c r="G152" t="n">
-        <v>1184.91</v>
+        <v>112.4</v>
       </c>
       <c r="H152" t="n">
-        <v>126.06</v>
+        <v>4.58</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[1964.03, 1964.03, 1964.03]</t>
+          <t>[1576.64, 2858.89, 2869.95]</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>[721.24, 726.03, 3037.98]</t>
+          <t>[1529.73, 2717.96, 2720.57]</t>
         </is>
       </c>
     </row>
@@ -7434,41 +7434,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1120.1</v>
+        <v>75.05</v>
       </c>
       <c r="G153" t="n">
-        <v>1118.81</v>
+        <v>56.97</v>
       </c>
       <c r="H153" t="n">
-        <v>107.54</v>
+        <v>2.08</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[1868.08, 1868.08, 1868.08]</t>
+          <t>[2762.33, 2725.01, 2860.96]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>[726.03, 3037.98, 823.6]</t>
+          <t>[2717.96, 2720.57, 2738.85]</t>
         </is>
       </c>
     </row>
@@ -7480,41 +7480,41 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1147.14</v>
+        <v>51.34</v>
       </c>
       <c r="G154" t="n">
-        <v>1140.07</v>
+        <v>35.71</v>
       </c>
       <c r="H154" t="n">
-        <v>121.98</v>
+        <v>1.28</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[1785.87, 1785.87, 1785.87]</t>
+          <t>[2705.11, 2826.32, 6676.07]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>[3037.98, 823.6, 580.03]</t>
+          <t>[2720.57, 2738.85, 6680.27]</t>
         </is>
       </c>
     </row>
@@ -7526,41 +7526,41 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1441.83</v>
+        <v>62.24</v>
       </c>
       <c r="G155" t="n">
-        <v>1389.82</v>
+        <v>54.84</v>
       </c>
       <c r="H155" t="n">
-        <v>129.56</v>
+        <v>3.46</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[1829.52, 1829.52, 1829.52]</t>
+          <t>[2833.57, 6704.77, 734.87]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>[823.6, 580.03, 3743.56]</t>
+          <t>[2738.85, 6680.27, 689.58]</t>
         </is>
       </c>
     </row>
@@ -7572,41 +7572,41 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1461.99</v>
+        <v>70.45</v>
       </c>
       <c r="G156" t="n">
-        <v>1403.6</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="H156" t="n">
-        <v>134.31</v>
+        <v>6.48</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[1767.13, 1767.13, 1767.13]</t>
+          <t>[6604.23, 716.3, 725.92]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>[580.03, 3743.56, 719.87]</t>
+          <t>[6680.27, 689.58, 634.31]</t>
         </is>
       </c>
     </row>
@@ -7618,17 +7618,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7637,22 +7637,22 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>192.86</v>
+        <v>170.87</v>
       </c>
       <c r="G157" t="n">
-        <v>162.18</v>
+        <v>135.25</v>
       </c>
       <c r="H157" t="n">
-        <v>8.23</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[3436.7, 655.33, 1414.59]</t>
+          <t>[719.77, 732.22, 3045.81]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>[3743.56, 719.87, 1529.73]</t>
+          <t>[689.58, 634.31, 3323.46]</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7683,22 +7683,22 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>10.95</v>
+        <v>222.01</v>
       </c>
       <c r="G158" t="n">
-        <v>8.01</v>
+        <v>154.25</v>
       </c>
       <c r="H158" t="n">
-        <v>0.92</v>
+        <v>8.34</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[701.62, 1529.05, 2723.04]</t>
+          <t>[719.47, 2948.48, 809.08]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>[719.87, 1529.73, 2717.96]</t>
+          <t>[634.31, 3323.46, 811.68]</t>
         </is>
       </c>
     </row>
@@ -7710,41 +7710,41 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>121.62</v>
+        <v>293.22</v>
       </c>
       <c r="G159" t="n">
-        <v>112.4</v>
+        <v>202.66</v>
       </c>
       <c r="H159" t="n">
-        <v>4.58</v>
+        <v>10.59</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[1576.64, 2858.89, 2869.95]</t>
+          <t>[2825.67, 801.67, 543.62]</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>[1529.73, 2717.96, 2720.57]</t>
+          <t>[3323.46, 811.68, 643.8]</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7756,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7771,26 +7771,26 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>75.05</v>
+        <v>318.16</v>
       </c>
       <c r="G160" t="n">
-        <v>56.97</v>
+        <v>203.9</v>
       </c>
       <c r="H160" t="n">
-        <v>2.08</v>
+        <v>7.41</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[2762.33, 2725.01, 2860.96]</t>
+          <t>[776.76, 616.31, 3472.56]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>[2717.96, 2720.57, 2738.85]</t>
+          <t>[811.68, 643.8, 4021.84]</t>
         </is>
       </c>
     </row>
@@ -7802,12 +7802,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7817,26 +7817,26 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>51.34</v>
+        <v>233.16</v>
       </c>
       <c r="G161" t="n">
-        <v>35.71</v>
+        <v>165.12</v>
       </c>
       <c r="H161" t="n">
-        <v>1.28</v>
+        <v>7.68</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[2705.11, 2826.32, 6676.07]</t>
+          <t>[614.91, 3625.11, 732.04]</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>[2720.57, 2738.85, 6680.27]</t>
+          <t>[643.8, 4021.84, 801.79]</t>
         </is>
       </c>
     </row>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7863,26 +7863,26 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>173.15</v>
+        <v>115.91</v>
       </c>
       <c r="G162" t="n">
-        <v>172.18</v>
+        <v>71.31</v>
       </c>
       <c r="H162" t="n">
-        <v>55.1</v>
+        <v>6.79</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[487.58, 487.58, 487.58]</t>
+          <t>[516.55, 1312.02, 625.96]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>[340.5, 297.1, 308.6]</t>
+          <t>[521.6, 1111.5, 617.6]</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7909,26 +7909,26 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>190.32</v>
+        <v>119.42</v>
       </c>
       <c r="G163" t="n">
-        <v>189.34</v>
+        <v>86.31</v>
       </c>
       <c r="H163" t="n">
-        <v>66.16</v>
+        <v>11.73</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[478.9, 478.9, 478.9]</t>
+          <t>[1312.02, 625.96, 367.04]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>[297.1, 308.6, 263.0]</t>
+          <t>[1111.5, 617.6, 317.0]</t>
         </is>
       </c>
     </row>
@@ -7940,12 +7940,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7955,26 +7955,26 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>201.85</v>
+        <v>29.29</v>
       </c>
       <c r="G164" t="n">
-        <v>199.52</v>
+        <v>19.51</v>
       </c>
       <c r="H164" t="n">
-        <v>54.34</v>
+        <v>5.72</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[468.14, 468.14, 468.14]</t>
+          <t>[625.96, 367.04, 441.18]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>[308.6, 263.0, 702.01]</t>
+          <t>[617.6, 317.0, 441.06]</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8001,26 +8001,26 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>267.42</v>
+        <v>28.91</v>
       </c>
       <c r="G165" t="n">
-        <v>260.4</v>
+        <v>17.35</v>
       </c>
       <c r="H165" t="n">
-        <v>50.64</v>
+        <v>5.46</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[459.35, 459.35, 459.35]</t>
+          <t>[367.04, 441.18, 340.5]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>[263.0, 702.01, 801.55]</t>
+          <t>[317.0, 441.06, 338.6]</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8047,26 +8047,26 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>276.64</v>
+        <v>1.72</v>
       </c>
       <c r="G166" t="n">
-        <v>269.37</v>
+        <v>1.44</v>
       </c>
       <c r="H166" t="n">
-        <v>53.88</v>
+        <v>0.46</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[448.35, 448.35, 448.35]</t>
+          <t>[441.18, 340.5, 297.1]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>[702.01, 801.55, 247.1]</t>
+          <t>[441.06, 338.6, 294.8]</t>
         </is>
       </c>
     </row>
@@ -8078,12 +8078,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8097,22 +8097,22 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>24.76</v>
+        <v>1.98</v>
       </c>
       <c r="G167" t="n">
-        <v>16.98</v>
+        <v>1.97</v>
       </c>
       <c r="H167" t="n">
-        <v>2.55</v>
+        <v>0.63</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[844.0, 243.66, 516.55]</t>
+          <t>[340.5, 297.1, 308.6]</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>[801.55, 247.1, 521.6]</t>
+          <t>[338.6, 294.8, 306.9]</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8143,22 +8143,22 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>115.82</v>
+        <v>1.79</v>
       </c>
       <c r="G168" t="n">
-        <v>69.67</v>
+        <v>1.73</v>
       </c>
       <c r="H168" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[243.66, 516.55, 1312.02]</t>
+          <t>[297.1, 308.6, 263.0]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>[247.1, 521.6, 1111.5]</t>
+          <t>[294.8, 306.9, 261.8]</t>
         </is>
       </c>
     </row>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8189,22 +8189,22 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>115.91</v>
+        <v>2.11</v>
       </c>
       <c r="G169" t="n">
-        <v>71.31</v>
+        <v>1.97</v>
       </c>
       <c r="H169" t="n">
-        <v>6.79</v>
+        <v>0.48</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[516.55, 1312.02, 625.96]</t>
+          <t>[308.6, 263.0, 702.01]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>[521.6, 1111.5, 617.6]</t>
+          <t>[306.9, 261.8, 699.0]</t>
         </is>
       </c>
     </row>
@@ -8216,12 +8216,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8235,22 +8235,22 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>119.42</v>
+        <v>4.64</v>
       </c>
       <c r="G170" t="n">
-        <v>86.31</v>
+        <v>3.85</v>
       </c>
       <c r="H170" t="n">
-        <v>11.73</v>
+        <v>0.6</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[1312.02, 625.96, 367.04]</t>
+          <t>[263.0, 702.01, 801.55]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>[1111.5, 617.6, 317.0]</t>
+          <t>[261.8, 699.0, 794.2]</t>
         </is>
       </c>
     </row>
@@ -8262,12 +8262,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8281,22 +8281,22 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>29.29</v>
+        <v>4.59</v>
       </c>
       <c r="G171" t="n">
-        <v>19.51</v>
+        <v>3.52</v>
       </c>
       <c r="H171" t="n">
-        <v>5.72</v>
+        <v>0.48</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[625.96, 367.04, 441.18]</t>
+          <t>[702.01, 801.55, 247.1]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>[617.6, 317.0, 441.06]</t>
+          <t>[699.0, 794.2, 246.9]</t>
         </is>
       </c>
     </row>
@@ -8308,41 +8308,41 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(2, 0, 5)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>48.34</v>
+        <v>46.08</v>
       </c>
       <c r="G172" t="n">
-        <v>46.23</v>
+        <v>33.98</v>
       </c>
       <c r="H172" t="n">
-        <v>11.53</v>
+        <v>4.36</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[417.51, 457.03, 549.27]</t>
+          <t>[723.0, 952.06, 688.25]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>[351.38, 419.37, 514.38]</t>
+          <t>[799.28, 949.76, 711.61]</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8373,22 +8373,22 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>41.83</v>
+        <v>23.05</v>
       </c>
       <c r="G173" t="n">
-        <v>35.19</v>
+        <v>22.56</v>
       </c>
       <c r="H173" t="n">
-        <v>5.25</v>
+        <v>2.64</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[400.86, 534.27, 832.62]</t>
+          <t>[978.77, 690.79, 899.05]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>[419.37, 514.38, 899.78]</t>
+          <t>[949.76, 711.61, 916.89]</t>
         </is>
       </c>
     </row>
@@ -8400,41 +8400,41 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>(2, 0, 2)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>60.9</v>
+        <v>81.23</v>
       </c>
       <c r="G174" t="n">
-        <v>57.15</v>
+        <v>58.76</v>
       </c>
       <c r="H174" t="n">
-        <v>7.59</v>
+        <v>4.48</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[542.41, 833.28, 851.72]</t>
+          <t>[708.09, 879.79, 1389.63]</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>[514.38, 899.78, 774.78]</t>
+          <t>[711.61, 916.89, 1525.3]</t>
         </is>
       </c>
     </row>
@@ -8446,41 +8446,41 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>(2, 0, 2)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>76.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="G175" t="n">
-        <v>75.84999999999999</v>
+        <v>70.75</v>
       </c>
       <c r="H175" t="n">
-        <v>8.35</v>
+        <v>7.75</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[817.93, 851.29, 1069.49]</t>
+          <t>[881.3, 1389.76, 350.92]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>[899.78, 774.78, 1138.67]</t>
+          <t>[916.89, 1525.3, 392.03]</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8511,22 +8511,22 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>72.09</v>
+        <v>112.56</v>
       </c>
       <c r="G176" t="n">
-        <v>58.38</v>
+        <v>85.45</v>
       </c>
       <c r="H176" t="n">
-        <v>6.68</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[880.46, 1072.24, 540.91]</t>
+          <t>[1336.36, 362.61, 385.63]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>[774.78, 1138.67, 537.89]</t>
+          <t>[1525.3, 392.03, 423.63]</t>
         </is>
       </c>
     </row>
@@ -8538,41 +8538,41 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>(2, 0, 2)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>76.22</v>
+        <v>32.34</v>
       </c>
       <c r="G177" t="n">
-        <v>61.27</v>
+        <v>32.19</v>
       </c>
       <c r="H177" t="n">
-        <v>6.31</v>
+        <v>7.35</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[1027.89, 539.13, 727.49]</t>
+          <t>[360.6, 387.32, 498.62]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>[1138.67, 537.89, 799.28]</t>
+          <t>[392.03, 423.63, 527.44]</t>
         </is>
       </c>
     </row>
@@ -8584,17 +8584,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(5, 0, 3)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8603,22 +8603,22 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>37.46</v>
+        <v>34.35</v>
       </c>
       <c r="G178" t="n">
-        <v>25.18</v>
+        <v>29.65</v>
       </c>
       <c r="H178" t="n">
-        <v>3.17</v>
+        <v>4.44</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[534.27, 734.94, 942.17]</t>
+          <t>[407.59, 508.66, 850.12]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>[537.89, 799.28, 949.76]</t>
+          <t>[423.63, 527.44, 904.24]</t>
         </is>
       </c>
     </row>
@@ -8630,17 +8630,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>(2, 0, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -8649,22 +8649,22 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>46.08</v>
+        <v>49.7</v>
       </c>
       <c r="G179" t="n">
-        <v>33.98</v>
+        <v>43.82</v>
       </c>
       <c r="H179" t="n">
-        <v>4.36</v>
+        <v>5.44</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[723.0, 952.06, 688.25]</t>
+          <t>[515.03, 853.9, 750.33]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>[799.28, 949.76, 711.61]</t>
+          <t>[527.44, 904.24, 819.04]</t>
         </is>
       </c>
     </row>
@@ -8676,17 +8676,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>(2, 0, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -8695,22 +8695,22 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>23.05</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G180" t="n">
-        <v>22.56</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="H180" t="n">
-        <v>2.64</v>
+        <v>6.9</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[978.77, 690.79, 899.05]</t>
+          <t>[860.44, 752.31, 1069.05]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>[949.76, 711.61, 916.89]</t>
+          <t>[904.24, 819.04, 1158.24]</t>
         </is>
       </c>
     </row>
@@ -8722,41 +8722,41 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>81.23</v>
+        <v>65.13</v>
       </c>
       <c r="G181" t="n">
-        <v>58.76</v>
+        <v>63.68</v>
       </c>
       <c r="H181" t="n">
-        <v>4.48</v>
+        <v>7.72</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[708.09, 879.79, 1389.63]</t>
+          <t>[764.55, 1075.21, 519.78]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>[711.61, 916.89, 1525.3]</t>
+          <t>[819.04, 1158.24, 573.3]</t>
         </is>
       </c>
     </row>
@@ -8768,12 +8768,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8787,22 +8787,22 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>11.56</v>
+        <v>32.45</v>
       </c>
       <c r="G182" t="n">
-        <v>11.4</v>
+        <v>32.4</v>
       </c>
       <c r="H182" t="n">
-        <v>10.95</v>
+        <v>6.25</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[290.82, 41.76, 187.6]</t>
+          <t>[1417.27, 661.12, 229.43]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>[299.48, 54.71, 200.2]</t>
+          <t>[1452.09, 692.96, 259.97]</t>
         </is>
       </c>
     </row>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8833,22 +8833,22 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>15.89</v>
+        <v>33.41</v>
       </c>
       <c r="G183" t="n">
-        <v>15.13</v>
+        <v>32.85</v>
       </c>
       <c r="H183" t="n">
-        <v>12.04</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[42.12, 189.3, 307.47]</t>
+          <t>[665.0, 230.8, 241.41]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>[54.71, 200.2, 285.56]</t>
+          <t>[692.96, 259.97, 282.85]</t>
         </is>
       </c>
     </row>
@@ -8860,12 +8860,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8879,22 +8879,22 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>43.9</v>
+        <v>30.69</v>
       </c>
       <c r="G184" t="n">
-        <v>37.45</v>
+        <v>30.01</v>
       </c>
       <c r="H184" t="n">
-        <v>11.43</v>
+        <v>9.85</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[205.78, 333.93, 459.15]</t>
+          <t>[233.19, 243.88, 419.36]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>[200.2, 285.56, 400.74]</t>
+          <t>[259.97, 282.85, 443.65]</t>
         </is>
       </c>
     </row>
@@ -8906,12 +8906,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8921,26 +8921,26 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>40.93</v>
+        <v>26.43</v>
       </c>
       <c r="G185" t="n">
-        <v>36.16</v>
+        <v>24.74</v>
       </c>
       <c r="H185" t="n">
-        <v>10.42</v>
+        <v>7.74</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[330.59, 454.67, 480.11]</t>
+          <t>[251.3, 432.06, 297.59]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>[285.56, 400.74, 470.6]</t>
+          <t>[282.85, 443.65, 328.67]</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8967,26 +8967,26 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>23.14</v>
+        <v>17.37</v>
       </c>
       <c r="G186" t="n">
-        <v>20.52</v>
+        <v>15.16</v>
       </c>
       <c r="H186" t="n">
-        <v>4.24</v>
+        <v>12.04</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[436.11, 459.98, 931.03]</t>
+          <t>[446.83, 307.69, 52.13]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>[400.74, 470.6, 946.59]</t>
+          <t>[443.65, 328.67, 73.46]</t>
         </is>
       </c>
     </row>
@@ -8998,12 +8998,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9013,26 +9013,26 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>41.11</v>
+        <v>22.38</v>
       </c>
       <c r="G187" t="n">
-        <v>37.97</v>
+        <v>22.35</v>
       </c>
       <c r="H187" t="n">
-        <v>4.01</v>
+        <v>15.45</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[450.38, 911.46, 1393.55]</t>
+          <t>[307.03, 52.01, 202.55]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>[470.6, 946.59, 1452.09]</t>
+          <t>[328.67, 73.46, 226.5]</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9059,26 +9059,26 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>35.64</v>
+        <v>19.18</v>
       </c>
       <c r="G188" t="n">
-        <v>34.79</v>
+        <v>19.12</v>
       </c>
       <c r="H188" t="n">
-        <v>3.6</v>
+        <v>13.95</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[921.82, 1408.44, 657.01]</t>
+          <t>[53.05, 206.57, 307.18]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>[946.59, 1452.09, 692.96]</t>
+          <t>[73.46, 226.5, 324.2]</t>
         </is>
       </c>
     </row>
@@ -9090,41 +9090,41 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>32.45</v>
+        <v>8.94</v>
       </c>
       <c r="G189" t="n">
-        <v>32.4</v>
+        <v>6.01</v>
       </c>
       <c r="H189" t="n">
-        <v>6.25</v>
+        <v>1.55</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[1417.27, 661.12, 229.43]</t>
+          <t>[224.5, 323.51, 446.98]</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>[1452.09, 692.96, 259.97]</t>
+          <t>[226.5, 324.2, 431.65]</t>
         </is>
       </c>
     </row>
@@ -9136,41 +9136,41 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>33.41</v>
+        <v>13.45</v>
       </c>
       <c r="G190" t="n">
-        <v>32.85</v>
+        <v>11.1</v>
       </c>
       <c r="H190" t="n">
-        <v>9.970000000000001</v>
+        <v>2.42</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[665.0, 230.8, 241.41]</t>
+          <t>[324.55, 448.21, 508.66]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>[692.96, 259.97, 282.85]</t>
+          <t>[324.2, 431.65, 492.27]</t>
         </is>
       </c>
     </row>
@@ -9182,41 +9182,41 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>30.69</v>
+        <v>18.98</v>
       </c>
       <c r="G191" t="n">
-        <v>30.01</v>
+        <v>18.68</v>
       </c>
       <c r="H191" t="n">
-        <v>9.85</v>
+        <v>3.15</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[233.19, 243.88, 419.36]</t>
+          <t>[448.06, 508.51, 1013.03]</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>[259.97, 282.85, 443.65]</t>
+          <t>[431.65, 492.27, 989.64]</t>
         </is>
       </c>
     </row>
@@ -9228,17 +9228,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9247,22 +9247,22 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1343</v>
+        <v>178.25</v>
       </c>
       <c r="G192" t="n">
-        <v>1328.2</v>
+        <v>173.95</v>
       </c>
       <c r="H192" t="n">
-        <v>27.33</v>
+        <v>4.29</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[6368.7, 6241.87, 5971.94]</t>
+          <t>[3565.05, 4410.95, 4565.29]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>[4865.05, 4811.11, 4921.76]</t>
+          <t>[3378.76, 4625.15, 4443.92]</t>
         </is>
       </c>
     </row>
@@ -9274,17 +9274,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>497.39</v>
+        <v>524.67</v>
       </c>
       <c r="G193" t="n">
-        <v>466.31</v>
+        <v>394.11</v>
       </c>
       <c r="H193" t="n">
-        <v>10.56</v>
+        <v>7.64</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[5097.01, 5335.08, 4733.01]</t>
+          <t>[4305.16, 4455.8, 4551.59]</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>[4811.11, 4921.76, 4033.29]</t>
+          <t>[4625.15, 4443.92, 5402.06]</t>
         </is>
       </c>
     </row>
@@ -9320,17 +9320,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9339,22 +9339,22 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>485.71</v>
+        <v>1589.52</v>
       </c>
       <c r="G194" t="n">
-        <v>433.23</v>
+        <v>1171.46</v>
       </c>
       <c r="H194" t="n">
-        <v>10.82</v>
+        <v>15.48</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[5051.31, 4562.01, 4477.43]</t>
+          <t>[4589.12, 4687.77, 6211.47]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>[4921.76, 4033.29, 3836.02]</t>
+          <t>[4443.92, 5402.06, 8866.36]</t>
         </is>
       </c>
     </row>
@@ -9366,17 +9366,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9385,22 +9385,22 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>503.66</v>
+        <v>1711.44</v>
       </c>
       <c r="G195" t="n">
-        <v>499.89</v>
+        <v>1453.72</v>
       </c>
       <c r="H195" t="n">
-        <v>11.83</v>
+        <v>21.47</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[4453.37, 4405.98, 4478.69]</t>
+          <t>[4631.11, 6136.39, 3587.74]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>[4033.29, 3836.02, 4988.31]</t>
+          <t>[5402.06, 8866.36, 4447.97]</t>
         </is>
       </c>
     </row>
@@ -9412,41 +9412,41 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>(2, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>649.66</v>
+        <v>1453.77</v>
       </c>
       <c r="G196" t="n">
-        <v>558.75</v>
+        <v>1181.62</v>
       </c>
       <c r="H196" t="n">
-        <v>17.06</v>
+        <v>17.85</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[3927.82, 4160.59, 3107.61]</t>
+          <t>[6489.75, 3794.34, 3752.27]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>[3836.02, 4988.31, 2350.88]</t>
+          <t>[8866.36, 4447.97, 4266.88]</t>
         </is>
       </c>
     </row>
@@ -9458,41 +9458,41 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>(2, 1, 0)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>684.1900000000001</v>
+        <v>421.07</v>
       </c>
       <c r="G197" t="n">
-        <v>627.9400000000001</v>
+        <v>320.62</v>
       </c>
       <c r="H197" t="n">
-        <v>18.9</v>
+        <v>7.16</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[4093.34, 3084.55, 3633.92]</t>
+          <t>[4379.68, 4460.7, 5239.99]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>[4988.31, 2350.88, 3378.76]</t>
+          <t>[4447.97, 4266.88, 4540.22]</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9519,26 +9519,26 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>790.62</v>
+        <v>467.04</v>
       </c>
       <c r="G198" t="n">
-        <v>740.01</v>
+        <v>382.36</v>
       </c>
       <c r="H198" t="n">
-        <v>25.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[3474.3, 3850.0, 5250.51]</t>
+          <t>[4507.25, 5298.16, 3790.95]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>[2350.88, 3378.76, 4625.15]</t>
+          <t>[4266.88, 4540.22, 3939.72]</t>
         </is>
       </c>
     </row>
@@ -9550,17 +9550,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9569,22 +9569,22 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>178.25</v>
+        <v>402.25</v>
       </c>
       <c r="G199" t="n">
-        <v>173.95</v>
+        <v>385.34</v>
       </c>
       <c r="H199" t="n">
-        <v>4.29</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[3565.05, 4410.95, 4565.29]</t>
+          <t>[5088.77, 3635.38, 3328.77]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>[3378.76, 4625.15, 4443.92]</t>
+          <t>[4540.22, 3939.72, 3631.9]</t>
         </is>
       </c>
     </row>
@@ -9596,17 +9596,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(3, 1, 3)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9615,22 +9615,22 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>524.67</v>
+        <v>599.6900000000001</v>
       </c>
       <c r="G200" t="n">
-        <v>394.11</v>
+        <v>596.9400000000001</v>
       </c>
       <c r="H200" t="n">
-        <v>7.64</v>
+        <v>15.58</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[4305.16, 4455.8, 4551.59]</t>
+          <t>[3375.81, 3082.65, 4592.66]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>[4625.15, 4443.92, 5402.06]</t>
+          <t>[3939.72, 3631.9, 3915.0]</t>
         </is>
       </c>
     </row>
@@ -9642,17 +9642,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -9661,22 +9661,22 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1589.52</v>
+        <v>686.29</v>
       </c>
       <c r="G201" t="n">
-        <v>1171.46</v>
+        <v>524.73</v>
       </c>
       <c r="H201" t="n">
-        <v>15.48</v>
+        <v>14.51</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[4589.12, 4687.77, 6211.47]</t>
+          <t>[3428.08, 5065.2, 2356.32]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>[4443.92, 5402.06, 8866.36]</t>
+          <t>[3631.9, 3915.0, 2576.47]</t>
         </is>
       </c>
     </row>
